--- a/basedatos_partidas/salida/descompuestos/CT-08-04-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-050.xlsx
@@ -539,10 +539,10 @@
         <v>4.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="H10" t="n">
-        <v>5.46</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="11">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>16.83</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="15">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>22.61</v>
+        <v>25.34</v>
       </c>
       <c r="H24" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>22.84</v>
+        <v>25.59</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-04-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-050.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos de madera y laminados</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
